--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-visualization-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-visualization-easy.xlsx
@@ -463,13 +463,13 @@
         <v>Biểu đồ tròn (Pie Chart) hoặc Biểu đồ vành khuyên (Donut Chart) — so sánh tỷ lệ phần trăm trên tổng thể</v>
       </c>
       <c r="G2" t="str">
+        <v>Biểu đồ phân tán (Scatter Plot) — phân tích mối tương quan giữa hai biến số</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ dữ liệu</v>
+      </c>
+      <c r="I2" t="str">
         <v>Biểu đồ đường (Line Chart) — theo dõi xu hướng biến động dữ liệu theo thời gian</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Biểu đồ phân tán (Scatter Plot) — phân tích mối tương quan giữa hai biến số</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Biểu đồ bản đồ nhiệt (Heatmap) — trực quan hóa mật độ phân bổ dữ liệu</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>Line Chart là lựa chọn chuẩn mực để hiển thị dữ liệu dạng chuỗi thời gian (Time Series), giúp người xem dễ dàng nhận ra xu hướng (trends), tính chu kỳ (seasonality) của số liệu.</v>
       </c>
       <c r="F3" t="str">
+        <v>Hiển thị mối tương quan giữa cân nặng và chiều cao của các học sinh — mối tương quan hai biến</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Thể hiện mật độ tập trung dân số của các tỉnh thành trên bản đồ địa lý — phân bổ địa lý</v>
+      </c>
+      <c r="H3" t="str">
         <v>Trực quan hóa xu hướng tăng trưởng hoặc suy giảm của dữ liệu liên tục theo thời gian — theo dõi xu hướng thời gian</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>So sánh giá trị rời rạc của 10 cửa hàng khác nhau trong cùng một tháng — so sánh giá trị rời rạc</v>
       </c>
-      <c r="H3" t="str">
-        <v>Hiển thị mối tương quan giữa cân nặng và chiều cao của các học sinh — mối tương quan hai biến</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Thể hiện mật độ tập trung dân số của các tỉnh thành trên bản đồ địa lý — phân bổ địa lý</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Slicer trong PowerBI là bộ lọc giao diện tương tác (như chọn Năm, chọn Khu vực), giúp người xem chủ động lọc dữ liệu trên dashboard theo nhu cầu phân tích tức thời.</v>
       </c>
       <c r="F4" t="str">
+        <v>Là thuật toán dùng để nén kích thước của các hình ảnh biểu đồ cho nhẹ báo cáo — nén ảnh biểu đồ</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Là biểu đồ dùng để hiển thị sơ đồ phân cấp nhân sự của doanh nghiệp — sơ đồ nhân sự</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Là công cụ dùng để cắt nhỏ file báo cáo ra thành nhiều tệp tin PDF độc lập — cắt nhỏ báo cáo</v>
+      </c>
+      <c r="I4" t="str">
         <v>Là bộ lọc trực quan cho phép người dùng tương tác bấm chọn để lọc dữ liệu hiển thị trên các biểu đồ khác — bộ lọc tương tác</v>
       </c>
-      <c r="G4" t="str">
-        <v>Là công cụ dùng để cắt nhỏ file báo cáo ra thành nhiều tệp tin PDF độc lập — cắt nhỏ báo cáo</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Là thuật toán dùng để nén kích thước của các hình ảnh biểu đồ cho nhẹ báo cáo — nén ảnh biểu đồ</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Là biểu đồ dùng để hiển thị sơ đồ phân cấp nhân sự của doanh nghiệp — sơ đồ nhân sự</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -588,19 +588,19 @@
         <v>Scatter Plot (Biểu đồ phân tán) hiển thị các giá trị dưới dạng các điểm chấm trên trục X và Y. Xu hướng phân bổ của các dấu chấm giúp nhận diện mối quan hệ tương quan tuyến tính (dương, âm hoặc không tương quan).</v>
       </c>
       <c r="F6" t="str">
+        <v>Biểu đồ cột chồng (Stacked Bar Chart) — so sánh các phần tử trong tổng số</v>
+      </c>
+      <c r="G6" t="str">
         <v>Biểu đồ phân tán (Scatter Plot) — biểu thị các cặp điểm dữ liệu trên hệ tọa độ đề-các</v>
       </c>
-      <c r="G6" t="str">
-        <v>Biểu đồ cột chồng (Stacked Bar Chart) — so sánh các phần tử trong tổng số</v>
-      </c>
       <c r="H6" t="str">
+        <v>Biểu đồ phễu (Funnel Chart) — theo dõi quy trình chuyển đổi khách hàng</v>
+      </c>
+      <c r="I6" t="str">
         <v>Biểu đồ tròn (Pie Chart) — so sánh tỷ lệ phần trăm đóng góp</v>
       </c>
-      <c r="I6" t="str">
-        <v>Biểu đồ phễu (Funnel Chart) — theo dõi quy trình chuyển đổi khách hàng</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Nguyên tắc của Edward Tufte khuyên tối đa hóa Data-to-Ink ratio. Nghĩa là phần lớn lượng "mực" (màu sắc, pixel trên màn hình) dùng để vẽ biểu đồ phải đại diện trực tiếp cho dữ liệu, tránh trang trí rườm rà (chartjunk) gây xao nhãng.</v>
       </c>
       <c r="F7" t="str">
+        <v>Chỉ hiển thị số liệu dưới dạng bảng văn bản thô đen trắng không có biểu đồ — tối giản hóa cực đoan</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Bắt buộc phải in tất cả các báo cáo ra giấy bằng mực in màu chất lượng cao nhất — in ấn vật lý báo cáo</v>
+      </c>
+      <c r="H7" t="str">
         <v>Tối giản hóa thiết kế bằng cách loại bỏ các yếu tố đồ họa thừa thãi (đường lưới quá đậm, hình vẽ 3D, viền bảng) để tập trung làm nổi bật dữ liệu chính — tối đa hóa hiển thị dữ liệu sạch</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Tăng cường sử dụng nhiều màu sắc rực rỡ và hình vẽ minh họa để lấp đầy khoảng trắng của biểu đồ — tăng mực in trang trí</v>
       </c>
-      <c r="H7" t="str">
-        <v>Bắt buộc phải in tất cả các báo cáo ra giấy bằng mực in màu chất lượng cao nhất — in ấn vật lý báo cáo</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Chỉ hiển thị số liệu dưới dạng bảng văn bản thô đen trắng không có biểu đồ — tối giản hóa cực đoan</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -687,13 +687,13 @@
         <v>Hiển thị một con số thống kê quan trọng duy nhất (như Tổng doanh thu, Số khách hàng mới) một cách nổi bật để người dùng dễ đọc nhanh — hiển thị chỉ số cốt lõi</v>
       </c>
       <c r="G9" t="str">
+        <v>Bảng danh sách tất cả các công việc hàng ngày của lập trình viên — danh sách tác vụ</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Biểu đồ hình cột thể hiện mức lương trung bình của nhân viên trong công ty — biểu đồ lương</v>
+      </c>
+      <c r="I9" t="str">
         <v>Dùng để khách hàng quẹt thẻ thanh toán chi phí mua hàng trực tiếp trên website — cổng thanh toán trực quan</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Bảng danh sách tất cả các công việc hàng ngày của lập trình viên — danh sách tác vụ</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Biểu đồ hình cột thể hiện mức lương trung bình của nhân viên trong công ty — biểu đồ lương</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -716,19 +716,19 @@
         <v>`CALCULATE` là hàm quan trọng và mạnh mẽ nhất trong DAX. Nó cho phép thay đổi ngữ cảnh bộ lọc (Filter Context) hiện tại để chạy các phép tính phức tạp với các điều kiện lọc mới.</v>
       </c>
       <c r="F10" t="str">
+        <v>SUM() — hàm tính tổng đơn giản của tất cả các giá trị trong một cột dữ liệu — tính tổng cột</v>
+      </c>
+      <c r="G10" t="str">
+        <v>AVERAGE() — hàm tính giá trị trung bình cộng đơn giản của cột số — tính trung bình</v>
+      </c>
+      <c r="H10" t="str">
+        <v>RELATED() — hàm lấy dữ liệu từ một bảng khác có liên kết khóa ngoại — lấy dữ liệu bảng liên kết</v>
+      </c>
+      <c r="I10" t="str">
         <v>CALCULATE() — hàm thay đổi ngữ cảnh bộ lọc để thực hiện phép tính tùy chỉnh — hàm thay đổi ngữ cảnh bộ lọc</v>
       </c>
-      <c r="G10" t="str">
-        <v>SUM() — hàm tính tổng đơn giản của tất cả các giá trị trong một cột dữ liệu — tính tổng cột</v>
-      </c>
-      <c r="H10" t="str">
-        <v>AVERAGE() — hàm tính giá trị trung bình cộng đơn giản của cột số — tính trung bình</v>
-      </c>
-      <c r="I10" t="str">
-        <v>RELATED() — hàm lấy dữ liệu từ một bảng khác có liên kết khóa ngoại — lấy dữ liệu bảng liên kết</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Việc cắt ngắn trục Y (ví dụ bắt đầu từ 90 đến 100 thay vì từ 0) trong biểu đồ cột sẽ phóng đại sự khác biệt một cách trực quan, khiến người xem tưởng rằng giá trị này gấp nhiều lần giá trị kia, vi phạm đạo đức trực quan hóa dữ liệu.</v>
       </c>
       <c r="F11" t="str">
+        <v>Bắt buộc phải ẩn hoàn toàn các nhãn tên danh mục ở trục hoành để giao diện gọn gàng — ẩn nhãn trục</v>
+      </c>
+      <c r="G11" t="str">
         <v>Trục giá trị (thường là trục Y) bắt buộc phải bắt đầu từ vạch số 0 (Zero baseline) để tránh gây hiểu lầm về mức độ chênh lệch — trục giá trị bắt đầu từ số 0</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Trục giá trị phải bắt đầu từ giá trị nhỏ nhất của bộ mẫu dữ liệu để kéo giãn cột ra — kéo giãn cột phóng đại</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Bắt buộc phải ẩn hoàn toàn các nhãn tên danh mục ở trục hoành để giao diện gọn gàng — ẩn nhãn trục</v>
       </c>
       <c r="I11" t="str">
         <v>Trục giá trị phải hiển thị theo thang đo logarit đối với tất cả các dạng số liệu — thang đo logarit bắt buộc</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
